--- a/artfynd/A 23130-2025 artfynd.xlsx
+++ b/artfynd/A 23130-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5393306</v>
+        <v>4443919</v>
       </c>
       <c r="B2" t="n">
-        <v>98537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222886</v>
+        <v>221903</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502414.0107225732</v>
+        <v>502414</v>
       </c>
       <c r="R2" t="n">
-        <v>6474941.819976112</v>
+        <v>6474942</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1973-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1977-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,12 +781,7 @@
         <v>5130460</v>
       </c>
       <c r="B3" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502414.0107225732</v>
+        <v>502414</v>
       </c>
       <c r="R3" t="n">
-        <v>6474941.819976112</v>
+        <v>6474942</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -866,19 +846,9 @@
           <t>1973-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1977-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -911,37 +881,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4443919</v>
+        <v>5393306</v>
       </c>
       <c r="B4" t="n">
-        <v>104033</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>222886</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502414.0107225732</v>
+        <v>502414</v>
       </c>
       <c r="R4" t="n">
-        <v>6474941.819976112</v>
+        <v>6474942</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -984,19 +949,9 @@
           <t>1973-06-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1977-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 23130-2025 artfynd.xlsx
+++ b/artfynd/A 23130-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4443919</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5130460</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,8 +996,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5393306</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>